--- a/Omakase_Ratings.xlsx
+++ b/Omakase_Ratings.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Omakase" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Omakase" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P202"/>
+  <dimension ref="A1:Q202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,7 @@
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="8" customWidth="1" min="15" max="15"/>
     <col width="35" customWidth="1" min="16" max="16"/>
+    <col width="60" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -532,6 +533,11 @@
       <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Google Maps Name</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Excluded Sources</t>
         </is>
       </c>
     </row>
@@ -572,13 +578,13 @@
         <v>4.102</v>
       </c>
       <c r="L2" t="n">
-        <v>36.5</v>
+        <v>37.6</v>
       </c>
       <c r="M2" t="n">
         <v>4.056</v>
       </c>
       <c r="N2" t="n">
-        <v>30.3</v>
+        <v>32.6</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -586,6 +592,7 @@
           <t>Hatsuhana</t>
         </is>
       </c>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -624,13 +631,13 @@
         <v>3.47</v>
       </c>
       <c r="L3" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="M3" t="n">
         <v>3.488</v>
       </c>
       <c r="N3" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -638,6 +645,7 @@
           <t>AKIMORI</t>
         </is>
       </c>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -676,13 +684,13 @@
         <v>4.099</v>
       </c>
       <c r="L4" t="n">
-        <v>35.5</v>
+        <v>36.6</v>
       </c>
       <c r="M4" t="n">
         <v>4.099</v>
       </c>
       <c r="N4" t="n">
-        <v>34.4</v>
+        <v>37.5</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -690,6 +698,7 @@
           <t>Gosuke</t>
         </is>
       </c>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -724,13 +733,13 @@
         <v>3.822</v>
       </c>
       <c r="L5" t="n">
-        <v>10.2</v>
+        <v>10.8</v>
       </c>
       <c r="M5" t="n">
         <v>3.842</v>
       </c>
       <c r="N5" t="n">
-        <v>17.4</v>
+        <v>18.5</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -738,6 +747,7 @@
           <t>Hōseki</t>
         </is>
       </c>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -769,21 +779,26 @@
         <v>271</v>
       </c>
       <c r="K6" t="n">
-        <v>4.014</v>
+        <v>3.723</v>
       </c>
       <c r="L6" t="n">
-        <v>24.9</v>
+        <v>5.9</v>
       </c>
       <c r="M6" t="n">
-        <v>3.941</v>
+        <v>3.656</v>
       </c>
       <c r="N6" t="n">
-        <v>24.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Omakase Shihou - Upper West Side (Lunch Available)</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Google rating 4.7 excluded — Google returned 'Omakase Shihou - Upper West Side (Lunch Available)', whose name similarity to 'Inase' is 0.13 — below the 0.80 trust threshold</t>
         </is>
       </c>
     </row>
@@ -820,13 +835,13 @@
         <v>4.293</v>
       </c>
       <c r="L7" t="n">
-        <v>65</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="M7" t="n">
         <v>4.123</v>
       </c>
       <c r="N7" t="n">
-        <v>36.9</v>
+        <v>39.7</v>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -834,6 +849,7 @@
           <t>Kizuna</t>
         </is>
       </c>
+      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -869,21 +885,26 @@
         <v>215</v>
       </c>
       <c r="K8" t="n">
-        <v>4.278</v>
+        <v>4.035</v>
       </c>
       <c r="L8" t="n">
-        <v>59.9</v>
+        <v>28.5</v>
       </c>
       <c r="M8" t="n">
-        <v>4.328</v>
+        <v>4.082</v>
       </c>
       <c r="N8" t="n">
-        <v>62.6</v>
+        <v>34.8</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Omakase by Kun Tsuki</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Google rating 4.9 excluded — Google returned 'Omakase by Kun Tsuki', whose name similarity to 'Kun Tsuki Omakase' is 0.50 — below the 0.80 trust threshold</t>
         </is>
       </c>
     </row>
@@ -924,13 +945,13 @@
         <v>4.241</v>
       </c>
       <c r="L9" t="n">
-        <v>54.3</v>
+        <v>55.4</v>
       </c>
       <c r="M9" t="n">
         <v>4.783</v>
       </c>
       <c r="N9" t="n">
-        <v>99</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -938,6 +959,7 @@
           <t>Mari.ne Handroll</t>
         </is>
       </c>
+      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -964,6 +986,7 @@
       <c r="H10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -998,13 +1021,13 @@
         <v>3.861</v>
       </c>
       <c r="L11" t="n">
-        <v>15.7</v>
+        <v>16.7</v>
       </c>
       <c r="M11" t="n">
         <v>3.953</v>
       </c>
       <c r="N11" t="n">
-        <v>25.1</v>
+        <v>26.6</v>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1012,6 +1035,7 @@
           <t>Nare Sushi</t>
         </is>
       </c>
+      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1046,13 +1070,13 @@
         <v>4.504</v>
       </c>
       <c r="L12" t="n">
-        <v>94.40000000000001</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="M12" t="n">
         <v>4.562</v>
       </c>
       <c r="N12" t="n">
-        <v>86.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -1060,6 +1084,7 @@
           <t>Omakase 33</t>
         </is>
       </c>
+      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1094,22 +1119,15 @@
       <c r="J13" t="n">
         <v>166</v>
       </c>
-      <c r="K13" t="n">
-        <v>4.332</v>
-      </c>
-      <c r="L13" t="n">
-        <v>75.09999999999999</v>
-      </c>
-      <c r="M13" t="n">
-        <v>4.311</v>
-      </c>
-      <c r="N13" t="n">
-        <v>60.5</v>
-      </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Omakase Shihou (Shiro) - Midtown</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Google rating 4.7 excluded — Google returned 'Omakase Shihou (Shiro) - Midtown', whose name similarity to 'Shihou Omakase' is 0.37 — below the 0.80 trust threshold</t>
         </is>
       </c>
     </row>
@@ -1150,13 +1168,13 @@
         <v>4.281</v>
       </c>
       <c r="L14" t="n">
-        <v>60.9</v>
+        <v>62.4</v>
       </c>
       <c r="M14" t="n">
         <v>4.45</v>
       </c>
       <c r="N14" t="n">
-        <v>74.90000000000001</v>
+        <v>74.5</v>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -1164,6 +1182,7 @@
           <t>SHOGUN OMAKASE | Manhattan Sushi Restaurant</t>
         </is>
       </c>
+      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1202,13 +1221,13 @@
         <v>4.09</v>
       </c>
       <c r="L15" t="n">
-        <v>34</v>
+        <v>34.9</v>
       </c>
       <c r="M15" t="n">
         <v>4.09</v>
       </c>
       <c r="N15" t="n">
-        <v>33.3</v>
+        <v>37</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -1216,6 +1235,7 @@
           <t>Sushi Beauu</t>
         </is>
       </c>
+      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1254,13 +1274,13 @@
         <v>4.335</v>
       </c>
       <c r="L16" t="n">
-        <v>76.09999999999999</v>
+        <v>78</v>
       </c>
       <c r="M16" t="n">
         <v>4.274</v>
       </c>
       <c r="N16" t="n">
-        <v>56.4</v>
+        <v>58.2</v>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
@@ -1268,6 +1288,7 @@
           <t>Sushi Kaito</t>
         </is>
       </c>
+      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1302,13 +1323,13 @@
         <v>4.076</v>
       </c>
       <c r="L17" t="n">
-        <v>31</v>
+        <v>31.7</v>
       </c>
       <c r="M17" t="n">
         <v>4.236</v>
       </c>
       <c r="N17" t="n">
-        <v>51.8</v>
+        <v>53.3</v>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
@@ -1316,6 +1337,7 @@
           <t>Sushi Masu</t>
         </is>
       </c>
+      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1354,13 +1376,13 @@
         <v>4.065</v>
       </c>
       <c r="L18" t="n">
-        <v>29.9</v>
+        <v>31.2</v>
       </c>
       <c r="M18" t="n">
         <v>3.855</v>
       </c>
       <c r="N18" t="n">
-        <v>20.5</v>
+        <v>22.3</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
@@ -1368,6 +1390,7 @@
           <t>Sushi Yasuda</t>
         </is>
       </c>
+      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1402,13 +1425,13 @@
         <v>4.289</v>
       </c>
       <c r="L19" t="n">
-        <v>64</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="M19" t="n">
         <v>4.248</v>
       </c>
       <c r="N19" t="n">
-        <v>53.8</v>
+        <v>56</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
@@ -1416,6 +1439,7 @@
           <t>Sushi You</t>
         </is>
       </c>
+      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1454,13 +1478,13 @@
         <v>4.001</v>
       </c>
       <c r="L20" t="n">
-        <v>22.8</v>
+        <v>24.2</v>
       </c>
       <c r="M20" t="n">
         <v>3.842</v>
       </c>
       <c r="N20" t="n">
-        <v>17.9</v>
+        <v>19</v>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
@@ -1468,6 +1492,7 @@
           <t>Trust Bae</t>
         </is>
       </c>
+      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1506,13 +1531,13 @@
         <v>4.427</v>
       </c>
       <c r="L21" t="n">
-        <v>87.3</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="M21" t="n">
         <v>4.692</v>
       </c>
       <c r="N21" t="n">
-        <v>94.90000000000001</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
@@ -1520,6 +1545,7 @@
           <t>Uka Omakase</t>
         </is>
       </c>
+      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1550,13 +1576,13 @@
         <v>4.055</v>
       </c>
       <c r="L22" t="n">
-        <v>29.4</v>
+        <v>30.6</v>
       </c>
       <c r="M22" t="n">
         <v>4.076</v>
       </c>
       <c r="N22" t="n">
-        <v>31.8</v>
+        <v>34.2</v>
       </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
@@ -1564,6 +1590,7 @@
           <t>UOGASHI</t>
         </is>
       </c>
+      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1602,13 +1629,13 @@
         <v>4.573</v>
       </c>
       <c r="L23" t="n">
-        <v>96.40000000000001</v>
+        <v>96.8</v>
       </c>
       <c r="M23" t="n">
         <v>4.538</v>
       </c>
       <c r="N23" t="n">
-        <v>85.09999999999999</v>
+        <v>84.8</v>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
@@ -1616,6 +1643,7 @@
           <t>Zama Omakase</t>
         </is>
       </c>
+      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1654,13 +1682,13 @@
         <v>4.155</v>
       </c>
       <c r="L24" t="n">
-        <v>42.1</v>
+        <v>43.5</v>
       </c>
       <c r="M24" t="n">
         <v>4.155</v>
       </c>
       <c r="N24" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
@@ -1668,6 +1696,7 @@
           <t>The Chemistry Room</t>
         </is>
       </c>
+      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1703,21 +1732,26 @@
         <v>672</v>
       </c>
       <c r="K25" t="n">
-        <v>4.647</v>
+        <v>4.713</v>
       </c>
       <c r="L25" t="n">
-        <v>98</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>4.701</v>
+        <v>4.769</v>
       </c>
       <c r="N25" t="n">
-        <v>95.90000000000001</v>
+        <v>97.8</v>
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Omakase by korami</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Google rating 4.8 excluded — Google returned 'Omakase by korami', whose name similarity to 'Korami Omakase' is 0.50 — below the 0.80 trust threshold</t>
         </is>
       </c>
     </row>
@@ -1752,16 +1786,17 @@
         <v>3.768</v>
       </c>
       <c r="L26" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="M26" t="n">
         <v>3.808</v>
       </c>
       <c r="N26" t="n">
-        <v>14.4</v>
+        <v>15.2</v>
       </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1800,13 +1835,13 @@
         <v>4.499</v>
       </c>
       <c r="L27" t="n">
-        <v>93.90000000000001</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="M27" t="n">
         <v>4.383</v>
       </c>
       <c r="N27" t="n">
-        <v>66.2</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
@@ -1814,6 +1849,7 @@
           <t>Sushiichi</t>
         </is>
       </c>
+      <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1852,13 +1888,13 @@
         <v>3.984</v>
       </c>
       <c r="L28" t="n">
-        <v>22.3</v>
+        <v>23.7</v>
       </c>
       <c r="M28" t="n">
         <v>4.193</v>
       </c>
       <c r="N28" t="n">
-        <v>46.7</v>
+        <v>48.9</v>
       </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
@@ -1866,6 +1902,7 @@
           <t>Sushi Lab Rooftop</t>
         </is>
       </c>
+      <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1904,13 +1941,13 @@
         <v>4.259</v>
       </c>
       <c r="L29" t="n">
-        <v>57.4</v>
+        <v>59.1</v>
       </c>
       <c r="M29" t="n">
         <v>4.584</v>
       </c>
       <c r="N29" t="n">
-        <v>88.7</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
@@ -1918,6 +1955,7 @@
           <t>Sendo</t>
         </is>
       </c>
+      <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1952,13 +1990,13 @@
         <v>3.962</v>
       </c>
       <c r="L30" t="n">
-        <v>20.8</v>
+        <v>21.5</v>
       </c>
       <c r="M30" t="n">
         <v>4.192</v>
       </c>
       <c r="N30" t="n">
-        <v>46.2</v>
+        <v>48.4</v>
       </c>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
@@ -1966,6 +2004,7 @@
           <t>Sushi Sasabune</t>
         </is>
       </c>
+      <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2004,13 +2043,13 @@
         <v>4.352</v>
       </c>
       <c r="L31" t="n">
-        <v>78.7</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="M31" t="n">
         <v>4.374</v>
       </c>
       <c r="N31" t="n">
-        <v>65.09999999999999</v>
+        <v>66.3</v>
       </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
@@ -2018,6 +2057,7 @@
           <t>Omakase SUSHI DAIRO</t>
         </is>
       </c>
+      <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2056,13 +2096,13 @@
         <v>4.323</v>
       </c>
       <c r="L32" t="n">
-        <v>72.09999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="M32" t="n">
         <v>4.565</v>
       </c>
       <c r="N32" t="n">
-        <v>87.2</v>
+        <v>87.5</v>
       </c>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
@@ -2070,6 +2110,7 @@
           <t>Tsumo Omakase</t>
         </is>
       </c>
+      <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2104,13 +2145,13 @@
         <v>4.567</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>95.40000000000001</v>
+        <v>95.7</v>
       </c>
       <c r="M33" s="2" t="n">
         <v>4.621</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>92.3</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2122,6 +2163,7 @@
           <t>One Bite Omakase</t>
         </is>
       </c>
+      <c r="Q33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2146,15 +2188,20 @@
         <v>128</v>
       </c>
       <c r="K34" t="n">
-        <v>4.069</v>
+        <v>3.804</v>
       </c>
       <c r="L34" t="n">
-        <v>30.5</v>
+        <v>9.1</v>
       </c>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>RokuNana</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>Google rating 4.8 excluded — Google returned 'RokuNana', whose name similarity to 'ROKI' is 0.50 — below the 0.80 trust threshold</t>
         </is>
       </c>
     </row>
@@ -2195,13 +2242,13 @@
         <v>4.283</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>62.4</v>
+        <v>63.4</v>
       </c>
       <c r="M35" s="2" t="n">
         <v>4.445</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>73.8</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2213,6 +2260,7 @@
           <t>SHINN EAST</t>
         </is>
       </c>
+      <c r="Q35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2251,13 +2299,13 @@
         <v>4.461</v>
       </c>
       <c r="L36" t="n">
-        <v>90.40000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="M36" t="n">
         <v>4.535</v>
       </c>
       <c r="N36" t="n">
-        <v>84.59999999999999</v>
+        <v>84.2</v>
       </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
@@ -2265,6 +2313,7 @@
           <t>Sushi Blossoms - Omakase Sushi in Chelsea NYC</t>
         </is>
       </c>
+      <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2300,21 +2349,26 @@
         <v>435</v>
       </c>
       <c r="K37" t="n">
-        <v>4.282</v>
+        <v>4.251</v>
       </c>
       <c r="L37" t="n">
-        <v>61.9</v>
+        <v>57</v>
       </c>
       <c r="M37" t="n">
-        <v>4.112</v>
+        <v>4.082</v>
       </c>
       <c r="N37" t="n">
-        <v>35.9</v>
+        <v>35.3</v>
       </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sushi By Bou - NOMAD NYC @ Hotel32|32</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Google rating 4.6 excluded — Google returned 'Sushi By Bou - NOMAD NYC @ Hotel32|32', whose name similarity to 'Sushi Suite 1001' is 0.39 — below the 0.80 trust threshold</t>
         </is>
       </c>
     </row>
@@ -2349,15 +2403,20 @@
         <v>832</v>
       </c>
       <c r="K38" t="n">
-        <v>3.725</v>
+        <v>3.148</v>
       </c>
       <c r="L38" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Sushi Tokyo Manhattan</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Google rating 4.7 excluded — Google returned 'Sushi Tokyo Manhattan', whose name similarity to 'Tokyo Bar' is 0.44 — below the 0.80 trust threshold</t>
         </is>
       </c>
     </row>
@@ -2398,13 +2457,13 @@
         <v>4.145</v>
       </c>
       <c r="L39" t="n">
-        <v>40.6</v>
+        <v>41.9</v>
       </c>
       <c r="M39" t="n">
         <v>4.781</v>
       </c>
       <c r="N39" t="n">
-        <v>98.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
@@ -2412,6 +2471,7 @@
           <t>KazuNori: The Original Hand Roll Bar</t>
         </is>
       </c>
+      <c r="Q39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2450,13 +2510,13 @@
         <v>3.835</v>
       </c>
       <c r="L40" t="n">
-        <v>11.2</v>
+        <v>11.8</v>
       </c>
       <c r="M40" t="n">
         <v>3.85</v>
       </c>
       <c r="N40" t="n">
-        <v>19.5</v>
+        <v>21.2</v>
       </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
@@ -2464,6 +2524,7 @@
           <t>Hasaki</t>
         </is>
       </c>
+      <c r="Q40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2502,13 +2563,13 @@
         <v>4.227</v>
       </c>
       <c r="L41" t="n">
-        <v>50.8</v>
+        <v>51.6</v>
       </c>
       <c r="M41" t="n">
         <v>4.282</v>
       </c>
       <c r="N41" t="n">
-        <v>57.9</v>
+        <v>59.8</v>
       </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
@@ -2516,6 +2577,7 @@
           <t>KAWA Omakase</t>
         </is>
       </c>
+      <c r="Q41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2551,21 +2613,26 @@
         <v>415</v>
       </c>
       <c r="K42" t="n">
-        <v>3.793</v>
+        <v>3.787</v>
       </c>
       <c r="L42" t="n">
         <v>8.6</v>
       </c>
       <c r="M42" t="n">
-        <v>3.793</v>
+        <v>3.787</v>
       </c>
       <c r="N42" t="n">
-        <v>13.3</v>
+        <v>13.6</v>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sushi Seki</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>Google rating 4.1 excluded — Google returned 'Sushi Seki', whose name similarity to 'Kissaki' is 0.25 — below the 0.80 trust threshold</t>
         </is>
       </c>
     </row>
@@ -2602,13 +2669,13 @@
         <v>4.149</v>
       </c>
       <c r="L43" t="n">
-        <v>41.1</v>
+        <v>42.5</v>
       </c>
       <c r="M43" t="n">
         <v>4.17</v>
       </c>
       <c r="N43" t="n">
-        <v>42.6</v>
+        <v>45.1</v>
       </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
@@ -2616,6 +2683,7 @@
           <t>Mayanoki</t>
         </is>
       </c>
+      <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2660,7 +2728,7 @@
         <v>4.725</v>
       </c>
       <c r="N44" t="n">
-        <v>96.90000000000001</v>
+        <v>96.2</v>
       </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
@@ -2668,6 +2736,7 @@
           <t>Mido - Omakase Room</t>
         </is>
       </c>
+      <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2702,13 +2771,13 @@
         <v>3.859</v>
       </c>
       <c r="L45" t="n">
-        <v>14.7</v>
+        <v>15.6</v>
       </c>
       <c r="M45" t="n">
         <v>3.879</v>
       </c>
       <c r="N45" t="n">
-        <v>21.5</v>
+        <v>23.4</v>
       </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
@@ -2716,6 +2785,7 @@
           <t>Moko</t>
         </is>
       </c>
+      <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2751,21 +2821,26 @@
         <v>59</v>
       </c>
       <c r="K46" t="n">
-        <v>4.052</v>
+        <v>3.689</v>
       </c>
       <c r="L46" t="n">
-        <v>27.9</v>
+        <v>4.8</v>
       </c>
       <c r="M46" t="n">
-        <v>4.17</v>
+        <v>3.797</v>
       </c>
       <c r="N46" t="n">
-        <v>42.1</v>
+        <v>14.7</v>
       </c>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Omakase By Tento</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>Google rating 5 excluded — Google returned 'Omakase By Tento', whose name similarity to 'Omakase by Teisui' is 0.76 — below the 0.80 trust threshold</t>
         </is>
       </c>
     </row>
@@ -2800,16 +2875,17 @@
         <v>3.333</v>
       </c>
       <c r="L47" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="M47" t="n">
         <v>3.508</v>
       </c>
       <c r="N47" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2844,13 +2920,13 @@
         <v>4.18</v>
       </c>
       <c r="L48" t="n">
-        <v>46.2</v>
+        <v>47.8</v>
       </c>
       <c r="M48" t="n">
         <v>4.285</v>
       </c>
       <c r="N48" t="n">
-        <v>58.5</v>
+        <v>60.3</v>
       </c>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
@@ -2858,6 +2934,7 @@
           <t>Sanyuu West</t>
         </is>
       </c>
+      <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2896,13 +2973,13 @@
         <v>4.571</v>
       </c>
       <c r="L49" t="n">
-        <v>95.90000000000001</v>
+        <v>96.2</v>
       </c>
       <c r="M49" t="n">
         <v>4.744</v>
       </c>
       <c r="N49" t="n">
-        <v>97.90000000000001</v>
+        <v>97.3</v>
       </c>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
@@ -2910,6 +2987,7 @@
           <t>Shinzo Omakase</t>
         </is>
       </c>
+      <c r="Q49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -2948,13 +3026,13 @@
         <v>3.72</v>
       </c>
       <c r="L50" s="2" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="M50" s="2" t="n">
         <v>3.728</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>10.3</v>
+        <v>10.9</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
@@ -2966,6 +3044,7 @@
           <t>SourAji</t>
         </is>
       </c>
+      <c r="Q50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3004,13 +3083,13 @@
         <v>4.117</v>
       </c>
       <c r="L51" t="n">
-        <v>37.6</v>
+        <v>38.7</v>
       </c>
       <c r="M51" t="n">
         <v>4.231</v>
       </c>
       <c r="N51" t="n">
-        <v>51.3</v>
+        <v>52.7</v>
       </c>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
@@ -3018,6 +3097,7 @@
           <t>SUGARFISH by sushi nozawa</t>
         </is>
       </c>
+      <c r="Q51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3056,7 +3136,7 @@
         <v>4.312</v>
       </c>
       <c r="L52" t="n">
-        <v>69.5</v>
+        <v>71.5</v>
       </c>
       <c r="M52" t="n">
         <v>4.502</v>
@@ -3070,6 +3150,7 @@
           <t>Sushi By Bou - East Village NYC</t>
         </is>
       </c>
+      <c r="Q52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3108,7 +3189,7 @@
         <v>4.354</v>
       </c>
       <c r="L53" t="n">
-        <v>79.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="M53" t="n">
         <v>4.519</v>
@@ -3122,6 +3203,7 @@
           <t>Sushi by M-East 5th st</t>
         </is>
       </c>
+      <c r="Q53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3160,13 +3242,13 @@
         <v>3.819</v>
       </c>
       <c r="L54" t="n">
-        <v>9.6</v>
+        <v>10.2</v>
       </c>
       <c r="M54" t="n">
         <v>3.827</v>
       </c>
       <c r="N54" t="n">
-        <v>15.9</v>
+        <v>16.8</v>
       </c>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
@@ -3174,6 +3256,7 @@
           <t>Sushi Dojo</t>
         </is>
       </c>
+      <c r="Q54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3212,13 +3295,13 @@
         <v>3.888</v>
       </c>
       <c r="L55" t="n">
-        <v>17.3</v>
+        <v>18.3</v>
       </c>
       <c r="M55" t="n">
         <v>3.818</v>
       </c>
       <c r="N55" t="n">
-        <v>14.9</v>
+        <v>15.8</v>
       </c>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
@@ -3226,6 +3309,7 @@
           <t>Sushi Seki</t>
         </is>
       </c>
+      <c r="Q55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3264,13 +3348,13 @@
         <v>4.332</v>
       </c>
       <c r="L56" t="n">
-        <v>75.59999999999999</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="M56" t="n">
         <v>4.459</v>
       </c>
       <c r="N56" t="n">
-        <v>76.40000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
@@ -3278,6 +3362,7 @@
           <t>Thirteen Water</t>
         </is>
       </c>
+      <c r="Q56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3316,13 +3401,13 @@
         <v>4.16</v>
       </c>
       <c r="L57" t="n">
-        <v>42.6</v>
+        <v>44.1</v>
       </c>
       <c r="M57" t="n">
         <v>4.085</v>
       </c>
       <c r="N57" t="n">
-        <v>32.3</v>
+        <v>35.9</v>
       </c>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
@@ -3330,6 +3415,7 @@
           <t>DOMODOMO New York</t>
         </is>
       </c>
+      <c r="Q57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3364,7 +3450,7 @@
         <v>4.362</v>
       </c>
       <c r="L58" t="n">
-        <v>81.2</v>
+        <v>82.8</v>
       </c>
       <c r="M58" t="n">
         <v>4.489</v>
@@ -3378,6 +3464,7 @@
           <t>Genki Omakase | Sushi • Japanese</t>
         </is>
       </c>
+      <c r="Q58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3422,7 +3509,7 @@
         <v>3.529</v>
       </c>
       <c r="N59" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
@@ -3430,6 +3517,7 @@
           <t>Kanoyama</t>
         </is>
       </c>
+      <c r="Q59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3468,7 +3556,7 @@
         <v>4.485</v>
       </c>
       <c r="L60" t="n">
-        <v>92.90000000000001</v>
+        <v>93</v>
       </c>
       <c r="M60" t="n">
         <v>4.616</v>
@@ -3482,6 +3570,7 @@
           <t>Kazumi Omakase</t>
         </is>
       </c>
+      <c r="Q60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3520,13 +3609,13 @@
         <v>4.658</v>
       </c>
       <c r="L61" t="n">
-        <v>98.5</v>
+        <v>97.8</v>
       </c>
       <c r="M61" t="n">
         <v>4.622</v>
       </c>
       <c r="N61" t="n">
-        <v>92.8</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
@@ -3534,6 +3623,7 @@
           <t>Nozomi NYC @Williamsburg</t>
         </is>
       </c>
+      <c r="Q61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3572,7 +3662,7 @@
         <v>3.685</v>
       </c>
       <c r="L62" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="M62" t="n">
         <v>3.634</v>
@@ -3586,6 +3676,7 @@
           <t>Saishin at Gansevoort Rooftop</t>
         </is>
       </c>
+      <c r="Q62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3624,13 +3715,13 @@
         <v>4.134</v>
       </c>
       <c r="L63" t="n">
-        <v>40.1</v>
+        <v>41.4</v>
       </c>
       <c r="M63" t="n">
         <v>3.909</v>
       </c>
       <c r="N63" t="n">
-        <v>23.1</v>
+        <v>25</v>
       </c>
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
@@ -3638,6 +3729,7 @@
           <t>Shota omakase</t>
         </is>
       </c>
+      <c r="Q63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3676,13 +3768,13 @@
         <v>3.9</v>
       </c>
       <c r="L64" t="n">
-        <v>17.8</v>
+        <v>18.8</v>
       </c>
       <c r="M64" t="n">
         <v>4.18</v>
       </c>
       <c r="N64" t="n">
-        <v>45.1</v>
+        <v>46.7</v>
       </c>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
@@ -3690,6 +3782,7 @@
           <t>Sushi Yashin</t>
         </is>
       </c>
+      <c r="Q64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3724,13 +3817,13 @@
         <v>4.326</v>
       </c>
       <c r="L65" t="n">
-        <v>73.09999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="M65" t="n">
         <v>4.289</v>
       </c>
       <c r="N65" t="n">
-        <v>59</v>
+        <v>60.9</v>
       </c>
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
@@ -3738,6 +3831,7 @@
           <t>U Omakase</t>
         </is>
       </c>
+      <c r="Q65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3776,13 +3870,13 @@
         <v>4.19</v>
       </c>
       <c r="L66" t="n">
-        <v>48.2</v>
+        <v>50</v>
       </c>
       <c r="M66" t="n">
         <v>4.313</v>
       </c>
       <c r="N66" t="n">
-        <v>61</v>
+        <v>62.5</v>
       </c>
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
@@ -3790,6 +3884,7 @@
           <t>Bondi Sushi</t>
         </is>
       </c>
+      <c r="Q66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3828,13 +3923,13 @@
         <v>4.184</v>
       </c>
       <c r="L67" t="n">
-        <v>47.2</v>
+        <v>48.9</v>
       </c>
       <c r="M67" t="n">
         <v>4.205</v>
       </c>
       <c r="N67" t="n">
-        <v>48.7</v>
+        <v>50.5</v>
       </c>
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
@@ -3842,6 +3937,7 @@
           <t>Douska</t>
         </is>
       </c>
+      <c r="Q67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3880,13 +3976,13 @@
         <v>4.319</v>
       </c>
       <c r="L68" t="n">
-        <v>71.59999999999999</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="M68" t="n">
         <v>4.489</v>
       </c>
       <c r="N68" t="n">
-        <v>80</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
@@ -3894,6 +3990,7 @@
           <t>Matsunori Handroll Bar</t>
         </is>
       </c>
+      <c r="Q68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3928,13 +4025,13 @@
         <v>4.257</v>
       </c>
       <c r="L69" t="n">
-        <v>56.3</v>
+        <v>58.1</v>
       </c>
       <c r="M69" t="n">
         <v>4.279</v>
       </c>
       <c r="N69" t="n">
-        <v>57.4</v>
+        <v>59.2</v>
       </c>
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
@@ -3942,6 +4039,7 @@
           <t>Mishik</t>
         </is>
       </c>
+      <c r="Q69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3976,13 +4074,13 @@
         <v>4.234</v>
       </c>
       <c r="L70" t="n">
-        <v>52.3</v>
+        <v>53.2</v>
       </c>
       <c r="M70" t="n">
         <v>4.388</v>
       </c>
       <c r="N70" t="n">
-        <v>67.2</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
@@ -3990,6 +4088,7 @@
           <t>Sushi 456</t>
         </is>
       </c>
+      <c r="Q70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4024,22 +4123,15 @@
       <c r="J71" t="n">
         <v>59</v>
       </c>
-      <c r="K71" t="n">
-        <v>4.385</v>
-      </c>
-      <c r="L71" t="n">
-        <v>83.5</v>
-      </c>
-      <c r="M71" t="n">
-        <v>4.394</v>
-      </c>
-      <c r="N71" t="n">
-        <v>69</v>
-      </c>
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Sushi Hayashi Williamsburg</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>Google rating 4.9 excluded — its Google place_id is claimed by another restaurant (both resolve to 'Sushi Hayashi Williamsburg'), so at least one match is wrong</t>
         </is>
       </c>
     </row>
@@ -4080,13 +4172,13 @@
         <v>4.238</v>
       </c>
       <c r="L72" t="n">
-        <v>52.8</v>
+        <v>53.8</v>
       </c>
       <c r="M72" t="n">
         <v>4.044</v>
       </c>
       <c r="N72" t="n">
-        <v>28.7</v>
+        <v>31</v>
       </c>
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
@@ -4094,6 +4186,7 @@
           <t>Sushi Nakazawa</t>
         </is>
       </c>
+      <c r="Q72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4132,13 +4225,13 @@
         <v>3.86</v>
       </c>
       <c r="L73" t="n">
-        <v>15.2</v>
+        <v>16.1</v>
       </c>
       <c r="M73" t="n">
         <v>4.076</v>
       </c>
       <c r="N73" t="n">
-        <v>31.3</v>
+        <v>33.7</v>
       </c>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
@@ -4146,6 +4239,7 @@
           <t>Sushi on Jones</t>
         </is>
       </c>
+      <c r="Q73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4184,13 +4278,13 @@
         <v>4.475</v>
       </c>
       <c r="L74" t="n">
-        <v>92.40000000000001</v>
+        <v>92.5</v>
       </c>
       <c r="M74" t="n">
         <v>4.479</v>
       </c>
       <c r="N74" t="n">
-        <v>77.90000000000001</v>
+        <v>77.7</v>
       </c>
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
@@ -4198,6 +4292,7 @@
           <t>Sushi On Me</t>
         </is>
       </c>
+      <c r="Q74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4236,13 +4331,13 @@
         <v>4.414</v>
       </c>
       <c r="L75" t="n">
-        <v>85.8</v>
+        <v>86</v>
       </c>
       <c r="M75" t="n">
         <v>4.465</v>
       </c>
       <c r="N75" t="n">
-        <v>76.90000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
@@ -4250,6 +4345,7 @@
           <t>TAKUMI OMAKASE</t>
         </is>
       </c>
+      <c r="Q75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4284,13 +4380,13 @@
         <v>4.123</v>
       </c>
       <c r="L76" t="n">
-        <v>38.6</v>
+        <v>39.8</v>
       </c>
       <c r="M76" t="n">
         <v>4.226</v>
       </c>
       <c r="N76" t="n">
-        <v>50.8</v>
+        <v>52.2</v>
       </c>
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
@@ -4298,6 +4394,7 @@
           <t>Ume</t>
         </is>
       </c>
+      <c r="Q76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4336,13 +4433,13 @@
         <v>4.052</v>
       </c>
       <c r="L77" t="n">
-        <v>28.4</v>
+        <v>29.6</v>
       </c>
       <c r="M77" t="n">
         <v>3.45</v>
       </c>
       <c r="N77" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
@@ -4350,6 +4447,7 @@
           <t>YOSHINO • NEW YORK</t>
         </is>
       </c>
+      <c r="Q77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4384,13 +4482,13 @@
         <v>4.433</v>
       </c>
       <c r="L78" t="n">
-        <v>87.8</v>
+        <v>88.2</v>
       </c>
       <c r="M78" t="n">
         <v>4.485</v>
       </c>
       <c r="N78" t="n">
-        <v>78.5</v>
+        <v>78.3</v>
       </c>
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
@@ -4398,6 +4496,7 @@
           <t>Zen Sushi Omakase</t>
         </is>
       </c>
+      <c r="Q78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4436,13 +4535,13 @@
         <v>4.277</v>
       </c>
       <c r="L79" t="n">
-        <v>59.4</v>
+        <v>61.3</v>
       </c>
       <c r="M79" t="n">
         <v>4.299</v>
       </c>
       <c r="N79" t="n">
-        <v>59.5</v>
+        <v>61.4</v>
       </c>
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
@@ -4450,6 +4549,7 @@
           <t>Sushi Ryusei</t>
         </is>
       </c>
+      <c r="Q79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4488,13 +4588,13 @@
         <v>4.173</v>
       </c>
       <c r="L80" t="n">
-        <v>44.2</v>
+        <v>45.2</v>
       </c>
       <c r="M80" t="n">
         <v>4.008</v>
       </c>
       <c r="N80" t="n">
-        <v>27.2</v>
+        <v>28.8</v>
       </c>
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
@@ -4502,6 +4602,7 @@
           <t>Blue Ribbon Sushi</t>
         </is>
       </c>
+      <c r="Q80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4540,13 +4641,13 @@
         <v>4.046</v>
       </c>
       <c r="L81" t="n">
-        <v>27.4</v>
+        <v>29</v>
       </c>
       <c r="M81" t="n">
         <v>4.088</v>
       </c>
       <c r="N81" t="n">
-        <v>32.8</v>
+        <v>36.4</v>
       </c>
       <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
@@ -4554,6 +4655,7 @@
           <t>Kintsugi Omakase</t>
         </is>
       </c>
+      <c r="Q81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4589,21 +4691,26 @@
         <v>306</v>
       </c>
       <c r="K82" t="n">
-        <v>4.349</v>
+        <v>4.31</v>
       </c>
       <c r="L82" t="n">
-        <v>78.2</v>
+        <v>71</v>
       </c>
       <c r="M82" t="n">
-        <v>4.221</v>
+        <v>4.183</v>
       </c>
       <c r="N82" t="n">
-        <v>50.3</v>
+        <v>47.3</v>
       </c>
       <c r="O82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Omakase room by Maaser</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>Google rating 4.7 excluded — Google returned 'Omakase room by Maaser', whose name similarity to 'Maaser Omakase' is 0.44 — below the 0.80 trust threshold</t>
         </is>
       </c>
     </row>
@@ -4644,13 +4751,13 @@
         <v>4.129</v>
       </c>
       <c r="L83" t="n">
-        <v>39.6</v>
+        <v>40.9</v>
       </c>
       <c r="M83" t="n">
         <v>3.965</v>
       </c>
       <c r="N83" t="n">
-        <v>25.6</v>
+        <v>27.2</v>
       </c>
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
@@ -4658,6 +4765,7 @@
           <t>Momoya SoHo</t>
         </is>
       </c>
+      <c r="Q83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4696,13 +4804,13 @@
         <v>4.006</v>
       </c>
       <c r="L84" t="n">
-        <v>23.4</v>
+        <v>24.7</v>
       </c>
       <c r="M84" t="n">
         <v>4.489</v>
       </c>
       <c r="N84" t="n">
-        <v>80.5</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
@@ -4710,6 +4818,7 @@
           <t>Nami Nori West Village</t>
         </is>
       </c>
+      <c r="Q84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4748,13 +4857,13 @@
         <v>4.296</v>
       </c>
       <c r="L85" t="n">
-        <v>66</v>
+        <v>67.2</v>
       </c>
       <c r="M85" t="n">
         <v>4.263</v>
       </c>
       <c r="N85" t="n">
-        <v>55.9</v>
+        <v>57.6</v>
       </c>
       <c r="O85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
@@ -4762,6 +4871,7 @@
           <t>Sekai Omakase</t>
         </is>
       </c>
+      <c r="Q85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -4800,13 +4910,13 @@
         <v>4.249</v>
       </c>
       <c r="L86" s="2" t="n">
-        <v>55.3</v>
+        <v>56.5</v>
       </c>
       <c r="M86" s="2" t="n">
         <v>4.436</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>73.3</v>
+        <v>72.8</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
@@ -4818,6 +4928,7 @@
           <t>Shiki Omakase</t>
         </is>
       </c>
+      <c r="Q86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4856,13 +4967,13 @@
         <v>3.953</v>
       </c>
       <c r="L87" t="n">
-        <v>20.3</v>
+        <v>21</v>
       </c>
       <c r="M87" t="n">
         <v>4.068</v>
       </c>
       <c r="N87" t="n">
-        <v>30.8</v>
+        <v>33.2</v>
       </c>
       <c r="O87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
@@ -4870,6 +4981,7 @@
           <t>Sushi By Bae</t>
         </is>
       </c>
+      <c r="Q87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4908,13 +5020,13 @@
         <v>4.319</v>
       </c>
       <c r="L88" t="n">
-        <v>71.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M88" t="n">
         <v>4.147</v>
       </c>
       <c r="N88" t="n">
-        <v>40</v>
+        <v>42.9</v>
       </c>
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
@@ -4922,6 +5034,7 @@
           <t>Sushi Ikumi</t>
         </is>
       </c>
+      <c r="Q88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4960,13 +5073,13 @@
         <v>4.231</v>
       </c>
       <c r="L89" t="n">
-        <v>51.3</v>
+        <v>52.2</v>
       </c>
       <c r="M89" t="n">
         <v>4.276</v>
       </c>
       <c r="N89" t="n">
-        <v>56.9</v>
+        <v>58.7</v>
       </c>
       <c r="O89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
@@ -4974,6 +5087,7 @@
           <t>Sushi Lin Upper West Side</t>
         </is>
       </c>
+      <c r="Q89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5012,13 +5126,13 @@
         <v>4.53</v>
       </c>
       <c r="L90" t="n">
-        <v>94.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="M90" t="n">
         <v>4.416</v>
       </c>
       <c r="N90" t="n">
-        <v>71.8</v>
+        <v>71.7</v>
       </c>
       <c r="O90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
@@ -5026,6 +5140,7 @@
           <t>Sushi Ouji</t>
         </is>
       </c>
+      <c r="Q90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5061,21 +5176,26 @@
         <v>260</v>
       </c>
       <c r="K91" t="n">
-        <v>4.317</v>
+        <v>4.18</v>
       </c>
       <c r="L91" t="n">
-        <v>70.59999999999999</v>
+        <v>47.3</v>
       </c>
       <c r="M91" t="n">
-        <v>4.388</v>
+        <v>4.248</v>
       </c>
       <c r="N91" t="n">
-        <v>66.7</v>
+        <v>55.4</v>
       </c>
       <c r="O91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Atto Sushi</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>Google rating 4.8 excluded — Google returned 'Atto Sushi', whose name similarity to 'Atto Omakase' is 0.50 — below the 0.80 trust threshold</t>
         </is>
       </c>
     </row>
@@ -5116,13 +5236,13 @@
         <v>3.851</v>
       </c>
       <c r="L92" t="n">
-        <v>13.7</v>
+        <v>14.5</v>
       </c>
       <c r="M92" t="n">
         <v>3.891</v>
       </c>
       <c r="N92" t="n">
-        <v>22.1</v>
+        <v>23.9</v>
       </c>
       <c r="O92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
@@ -5130,6 +5250,7 @@
           <t>Noz Market</t>
         </is>
       </c>
+      <c r="Q92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5168,13 +5289,13 @@
         <v>4.24</v>
       </c>
       <c r="L93" t="n">
-        <v>53.8</v>
+        <v>54.8</v>
       </c>
       <c r="M93" t="n">
         <v>4.544</v>
       </c>
       <c r="N93" t="n">
-        <v>85.59999999999999</v>
+        <v>85.3</v>
       </c>
       <c r="O93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
@@ -5182,6 +5303,7 @@
           <t>Oyishi Sushi 80 ST</t>
         </is>
       </c>
+      <c r="Q93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5220,13 +5342,13 @@
         <v>4.297</v>
       </c>
       <c r="L94" t="n">
-        <v>67</v>
+        <v>68.3</v>
       </c>
       <c r="M94" t="n">
         <v>4.14</v>
       </c>
       <c r="N94" t="n">
-        <v>39.5</v>
+        <v>42.4</v>
       </c>
       <c r="O94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
@@ -5234,6 +5356,7 @@
           <t>Sushi jin</t>
         </is>
       </c>
+      <c r="Q94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5272,13 +5395,13 @@
         <v>4.306</v>
       </c>
       <c r="L95" t="n">
-        <v>67.5</v>
+        <v>68.8</v>
       </c>
       <c r="M95" t="n">
         <v>4.246</v>
       </c>
       <c r="N95" t="n">
-        <v>53.3</v>
+        <v>54.9</v>
       </c>
       <c r="O95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
@@ -5286,6 +5409,7 @@
           <t>Sushi Koya</t>
         </is>
       </c>
+      <c r="Q95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5330,7 +5454,7 @@
         <v>4.697</v>
       </c>
       <c r="N96" t="n">
-        <v>95.40000000000001</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="O96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
@@ -5338,6 +5462,7 @@
           <t>Sushi YOLO</t>
         </is>
       </c>
+      <c r="Q96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5376,13 +5501,13 @@
         <v>4.355</v>
       </c>
       <c r="L97" t="n">
-        <v>79.7</v>
+        <v>81.2</v>
       </c>
       <c r="M97" t="n">
         <v>4.401</v>
       </c>
       <c r="N97" t="n">
-        <v>70.3</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="O97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
@@ -5390,6 +5515,7 @@
           <t>Tatsuda Omakase</t>
         </is>
       </c>
+      <c r="Q97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5424,13 +5550,13 @@
         <v>4.258</v>
       </c>
       <c r="L98" t="n">
-        <v>56.9</v>
+        <v>58.6</v>
       </c>
       <c r="M98" t="n">
         <v>4.382</v>
       </c>
       <c r="N98" t="n">
-        <v>65.59999999999999</v>
+        <v>66.8</v>
       </c>
       <c r="O98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
@@ -5438,6 +5564,7 @@
           <t>Fuku Omakase</t>
         </is>
       </c>
+      <c r="Q98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5472,13 +5599,13 @@
         <v>4.092</v>
       </c>
       <c r="L99" t="n">
-        <v>34.5</v>
+        <v>35.5</v>
       </c>
       <c r="M99" t="n">
         <v>4.113</v>
       </c>
       <c r="N99" t="n">
-        <v>36.4</v>
+        <v>39.1</v>
       </c>
       <c r="O99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
@@ -5486,6 +5613,7 @@
           <t>Hatsu Omakase</t>
         </is>
       </c>
+      <c r="Q99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5520,13 +5648,13 @@
         <v>4.283</v>
       </c>
       <c r="L100" t="n">
-        <v>62.9</v>
+        <v>64</v>
       </c>
       <c r="M100" t="n">
         <v>4.445</v>
       </c>
       <c r="N100" t="n">
-        <v>74.40000000000001</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="O100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
@@ -5534,6 +5662,7 @@
           <t>Kinzan Omakase</t>
         </is>
       </c>
+      <c r="Q100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5568,7 +5697,7 @@
         <v>4.439</v>
       </c>
       <c r="L101" t="n">
-        <v>88.8</v>
+        <v>89.2</v>
       </c>
       <c r="M101" t="n">
         <v>4.613</v>
@@ -5582,6 +5711,7 @@
           <t>Kyuubi Sushi Omakase</t>
         </is>
       </c>
+      <c r="Q101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5616,13 +5746,13 @@
         <v>4.006</v>
       </c>
       <c r="L102" t="n">
-        <v>23.9</v>
+        <v>25.3</v>
       </c>
       <c r="M102" t="n">
         <v>3.847</v>
       </c>
       <c r="N102" t="n">
-        <v>18.5</v>
+        <v>20.1</v>
       </c>
       <c r="O102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
@@ -5630,6 +5760,7 @@
           <t>Mitsuru</t>
         </is>
       </c>
+      <c r="Q102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5664,13 +5795,13 @@
         <v>4.307</v>
       </c>
       <c r="L103" t="n">
-        <v>68</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="M103" t="n">
         <v>4.572</v>
       </c>
       <c r="N103" t="n">
-        <v>88.2</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
@@ -5678,6 +5809,7 @@
           <t>Mojo East</t>
         </is>
       </c>
+      <c r="Q103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5716,13 +5848,13 @@
         <v>4.088</v>
       </c>
       <c r="L104" t="n">
-        <v>33</v>
+        <v>33.9</v>
       </c>
       <c r="M104" t="n">
         <v>3.998</v>
       </c>
       <c r="N104" t="n">
-        <v>26.7</v>
+        <v>28.3</v>
       </c>
       <c r="O104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
@@ -5730,6 +5862,7 @@
           <t>Mori</t>
         </is>
       </c>
+      <c r="Q104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5768,13 +5901,13 @@
         <v>4.012</v>
       </c>
       <c r="L105" t="n">
-        <v>24.4</v>
+        <v>25.8</v>
       </c>
       <c r="M105" t="n">
         <v>3.853</v>
       </c>
       <c r="N105" t="n">
-        <v>20</v>
+        <v>21.7</v>
       </c>
       <c r="O105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
@@ -5782,6 +5915,7 @@
           <t>Nobu Downtown</t>
         </is>
       </c>
+      <c r="Q105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5809,21 +5943,26 @@
         <v>236</v>
       </c>
       <c r="K106" t="n">
-        <v>4.2</v>
+        <v>3.979</v>
       </c>
       <c r="L106" t="n">
-        <v>49.7</v>
+        <v>23.1</v>
       </c>
       <c r="M106" t="n">
-        <v>4.254</v>
+        <v>4.03</v>
       </c>
       <c r="N106" t="n">
-        <v>54.4</v>
+        <v>30.4</v>
       </c>
       <c r="O106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Omakase Sushi by No name</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>Google rating 4.8 excluded — its Google place_id is claimed by another restaurant (both resolve to 'Omakase Sushi by No name'), so at least one match is wrong</t>
         </is>
       </c>
     </row>
@@ -5864,13 +6003,13 @@
         <v>4.616</v>
       </c>
       <c r="L107" t="n">
-        <v>97.5</v>
+        <v>97.3</v>
       </c>
       <c r="M107" t="n">
         <v>4.532</v>
       </c>
       <c r="N107" t="n">
-        <v>83.59999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="O107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
@@ -5878,6 +6017,7 @@
           <t>Sushi Saikou</t>
         </is>
       </c>
+      <c r="Q107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5909,21 +6049,26 @@
         <v>257</v>
       </c>
       <c r="K108" t="n">
-        <v>4.21</v>
+        <v>4.327</v>
       </c>
       <c r="L108" t="n">
-        <v>50.3</v>
+        <v>75.3</v>
       </c>
       <c r="M108" t="n">
-        <v>4.431</v>
+        <v>4.553</v>
       </c>
       <c r="N108" t="n">
-        <v>72.8</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="O108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Kawa Sushi</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>Google rating 4.4 excluded — Google returned 'Kawa Sushi', whose name similarity to 'Sake Kawa' is 0.47 — below the 0.80 trust threshold</t>
         </is>
       </c>
     </row>
@@ -5960,13 +6105,13 @@
         <v>4.2</v>
       </c>
       <c r="L109" t="n">
-        <v>49.2</v>
+        <v>51.1</v>
       </c>
       <c r="M109" t="n">
         <v>4.209</v>
       </c>
       <c r="N109" t="n">
-        <v>49.7</v>
+        <v>51.6</v>
       </c>
       <c r="O109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
@@ -5974,6 +6119,7 @@
           <t>Shh omakase</t>
         </is>
       </c>
+      <c r="Q109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -6008,13 +6154,13 @@
         <v>3.833</v>
       </c>
       <c r="L110" t="n">
-        <v>10.7</v>
+        <v>11.3</v>
       </c>
       <c r="M110" t="n">
         <v>3.841</v>
       </c>
       <c r="N110" t="n">
-        <v>16.9</v>
+        <v>17.9</v>
       </c>
       <c r="O110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
@@ -6022,6 +6168,7 @@
           <t>Shinsen oMAXkase &amp; Lounge</t>
         </is>
       </c>
+      <c r="Q110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -6056,13 +6203,13 @@
         <v>3.849</v>
       </c>
       <c r="L111" t="n">
-        <v>13.2</v>
+        <v>14</v>
       </c>
       <c r="M111" t="n">
         <v>4.051</v>
       </c>
       <c r="N111" t="n">
-        <v>29.2</v>
+        <v>31.5</v>
       </c>
       <c r="O111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
@@ -6070,6 +6217,7 @@
           <t>Shirokuro</t>
         </is>
       </c>
+      <c r="Q111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -6100,13 +6248,13 @@
         <v>4.233</v>
       </c>
       <c r="L112" t="n">
-        <v>51.8</v>
+        <v>52.7</v>
       </c>
       <c r="M112" t="n">
         <v>4.399</v>
       </c>
       <c r="N112" t="n">
-        <v>69.7</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="O112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
@@ -6114,6 +6262,7 @@
           <t>SHOSHIN 68</t>
         </is>
       </c>
+      <c r="Q112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -6148,22 +6297,15 @@
       <c r="J113" t="n">
         <v>761</v>
       </c>
-      <c r="K113" t="n">
-        <v>4.462</v>
-      </c>
-      <c r="L113" t="n">
-        <v>90.90000000000001</v>
-      </c>
-      <c r="M113" t="n">
-        <v>4.592</v>
-      </c>
-      <c r="N113" t="n">
-        <v>89.7</v>
-      </c>
       <c r="O113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Otani</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>Google rating 4.7 excluded — Google returned 'Otani', whose name similarity to 'Sushi Daizen' is 0.12 — below the 0.80 trust threshold</t>
         </is>
       </c>
     </row>
@@ -6204,13 +6346,13 @@
         <v>4.285</v>
       </c>
       <c r="L114" t="n">
-        <v>63.5</v>
+        <v>64.5</v>
       </c>
       <c r="M114" t="n">
         <v>4.355</v>
       </c>
       <c r="N114" t="n">
-        <v>64.09999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="O114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
@@ -6218,6 +6360,7 @@
           <t>Sushi Kai - West Village</t>
         </is>
       </c>
+      <c r="Q114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6256,13 +6399,13 @@
         <v>4.49</v>
       </c>
       <c r="L115" t="n">
-        <v>93.40000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="M115" t="n">
         <v>4.409</v>
       </c>
       <c r="N115" t="n">
-        <v>70.8</v>
+        <v>70.7</v>
       </c>
       <c r="O115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
@@ -6270,6 +6413,7 @@
           <t>Sushi Makoto - Omakase</t>
         </is>
       </c>
+      <c r="Q115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -6300,13 +6444,13 @@
         <v>4.385</v>
       </c>
       <c r="L116" t="n">
-        <v>84.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="M116" t="n">
         <v>4.457</v>
       </c>
       <c r="N116" t="n">
-        <v>75.90000000000001</v>
+        <v>75.5</v>
       </c>
       <c r="O116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
@@ -6314,6 +6458,7 @@
           <t>Taikun Sushi</t>
         </is>
       </c>
+      <c r="Q116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -6352,13 +6497,13 @@
         <v>4.263</v>
       </c>
       <c r="L117" t="n">
-        <v>57.9</v>
+        <v>59.7</v>
       </c>
       <c r="M117" t="n">
         <v>4.169</v>
       </c>
       <c r="N117" t="n">
-        <v>41.5</v>
+        <v>44.6</v>
       </c>
       <c r="O117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
@@ -6366,6 +6511,7 @@
           <t>TOWA</t>
         </is>
       </c>
+      <c r="Q117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -6397,21 +6543,26 @@
         <v>236</v>
       </c>
       <c r="K118" t="n">
-        <v>4.165</v>
+        <v>3.917</v>
       </c>
       <c r="L118" t="n">
-        <v>43.1</v>
+        <v>19.4</v>
       </c>
       <c r="M118" t="n">
-        <v>4.09</v>
+        <v>3.846</v>
       </c>
       <c r="N118" t="n">
-        <v>33.8</v>
+        <v>19.6</v>
       </c>
       <c r="O118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Omakase Sushi by No name</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>Google rating 4.8 excluded — its Google place_id is claimed by another restaurant (both resolve to 'Omakase Sushi by No name'), so at least one match is wrong</t>
         </is>
       </c>
     </row>
@@ -6448,13 +6599,13 @@
         <v>4.192</v>
       </c>
       <c r="L119" t="n">
-        <v>48.7</v>
+        <v>50.5</v>
       </c>
       <c r="M119" t="n">
         <v>4.242</v>
       </c>
       <c r="N119" t="n">
-        <v>52.3</v>
+        <v>53.8</v>
       </c>
       <c r="O119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
@@ -6462,6 +6613,7 @@
           <t>Yokox Omakase</t>
         </is>
       </c>
+      <c r="Q119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -6500,13 +6652,13 @@
         <v>3.813</v>
       </c>
       <c r="L120" t="n">
-        <v>9.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M120" t="n">
         <v>4.013</v>
       </c>
       <c r="N120" t="n">
-        <v>27.7</v>
+        <v>29.3</v>
       </c>
       <c r="O120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
@@ -6514,6 +6666,7 @@
           <t>Tsushima</t>
         </is>
       </c>
+      <c r="Q120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -6548,7 +6701,7 @@
         <v>4.345</v>
       </c>
       <c r="L121" t="n">
-        <v>77.2</v>
+        <v>79</v>
       </c>
       <c r="M121" t="n">
         <v>4.522</v>
@@ -6562,6 +6715,7 @@
           <t>IWAK Sushi + Kitchen</t>
         </is>
       </c>
+      <c r="Q121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -6596,13 +6750,13 @@
         <v>3.846</v>
       </c>
       <c r="L122" t="n">
-        <v>12.2</v>
+        <v>12.9</v>
       </c>
       <c r="M122" t="n">
         <v>3.761</v>
       </c>
       <c r="N122" t="n">
-        <v>12.3</v>
+        <v>12.5</v>
       </c>
       <c r="O122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
@@ -6610,6 +6764,7 @@
           <t>Junsui Omakase</t>
         </is>
       </c>
+      <c r="Q122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -6648,13 +6803,13 @@
         <v>4.088</v>
       </c>
       <c r="L123" t="n">
-        <v>32.5</v>
+        <v>33.3</v>
       </c>
       <c r="M123" t="n">
         <v>4.109</v>
       </c>
       <c r="N123" t="n">
-        <v>34.9</v>
+        <v>38</v>
       </c>
       <c r="O123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
@@ -6662,6 +6817,7 @@
           <t>Kinjo</t>
         </is>
       </c>
+      <c r="Q123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -6692,13 +6848,13 @@
         <v>4.1</v>
       </c>
       <c r="L124" t="n">
-        <v>36</v>
+        <v>37.1</v>
       </c>
       <c r="M124" t="n">
         <v>4.148</v>
       </c>
       <c r="N124" t="n">
-        <v>40.5</v>
+        <v>43.5</v>
       </c>
       <c r="O124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
@@ -6706,6 +6862,7 @@
           <t>LUYA Omakase &amp; Wine Bar</t>
         </is>
       </c>
+      <c r="Q124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -6736,13 +6893,13 @@
         <v>4.077</v>
       </c>
       <c r="L125" t="n">
-        <v>31.5</v>
+        <v>32.3</v>
       </c>
       <c r="M125" t="n">
         <v>4.196</v>
       </c>
       <c r="N125" t="n">
-        <v>47.2</v>
+        <v>49.5</v>
       </c>
       <c r="O125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
@@ -6750,6 +6907,7 @@
           <t>Miro Sushi</t>
         </is>
       </c>
+      <c r="Q125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -6788,13 +6946,13 @@
         <v>4.268</v>
       </c>
       <c r="L126" t="n">
-        <v>58.4</v>
+        <v>60.2</v>
       </c>
       <c r="M126" t="n">
         <v>4.455</v>
       </c>
       <c r="N126" t="n">
-        <v>75.40000000000001</v>
+        <v>75</v>
       </c>
       <c r="O126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
@@ -6802,6 +6960,7 @@
           <t>Neta Shari</t>
         </is>
       </c>
+      <c r="Q126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -6836,13 +6995,13 @@
         <v>4.331</v>
       </c>
       <c r="L127" t="n">
-        <v>74.09999999999999</v>
+        <v>76.3</v>
       </c>
       <c r="M127" t="n">
         <v>4.26</v>
       </c>
       <c r="N127" t="n">
-        <v>54.9</v>
+        <v>56.5</v>
       </c>
       <c r="O127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
@@ -6850,6 +7009,7 @@
           <t>Omakase sushi by hiro</t>
         </is>
       </c>
+      <c r="Q127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -6880,13 +7040,13 @@
         <v>4.092</v>
       </c>
       <c r="L128" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M128" t="n">
         <v>4.018</v>
       </c>
       <c r="N128" t="n">
-        <v>28.2</v>
+        <v>29.9</v>
       </c>
       <c r="O128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
@@ -6894,6 +7054,7 @@
           <t>SORA</t>
         </is>
       </c>
+      <c r="Q128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -6932,13 +7093,13 @@
         <v>4.028</v>
       </c>
       <c r="L129" t="n">
-        <v>26.4</v>
+        <v>27.4</v>
       </c>
       <c r="M129" t="n">
         <v>4.134</v>
       </c>
       <c r="N129" t="n">
-        <v>38.5</v>
+        <v>41.3</v>
       </c>
       <c r="O129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
@@ -6946,6 +7107,7 @@
           <t>Sushi Katsuei</t>
         </is>
       </c>
+      <c r="Q129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -6976,13 +7138,13 @@
         <v>3.686</v>
       </c>
       <c r="L130" t="n">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="M130" t="n">
         <v>3.794</v>
       </c>
       <c r="N130" t="n">
-        <v>13.8</v>
+        <v>14.1</v>
       </c>
       <c r="O130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
@@ -6990,6 +7152,7 @@
           <t>Sushi Uesugi</t>
         </is>
       </c>
+      <c r="Q130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -7020,13 +7183,13 @@
         <v>3.77</v>
       </c>
       <c r="L131" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="M131" t="n">
         <v>3.819</v>
       </c>
       <c r="N131" t="n">
-        <v>15.4</v>
+        <v>16.3</v>
       </c>
       <c r="O131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
@@ -7034,6 +7197,7 @@
           <t>Yamashiro</t>
         </is>
       </c>
+      <c r="Q131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -7068,13 +7232,13 @@
         <v>3.851</v>
       </c>
       <c r="L132" t="n">
-        <v>14.2</v>
+        <v>15.1</v>
       </c>
       <c r="M132" t="n">
         <v>4.316</v>
       </c>
       <c r="N132" t="n">
-        <v>61.5</v>
+        <v>63</v>
       </c>
       <c r="O132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
@@ -7082,6 +7246,7 @@
           <t>E Sushi II</t>
         </is>
       </c>
+      <c r="Q132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -7120,13 +7285,13 @@
         <v>3.168</v>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M133" t="n">
         <v>3.288</v>
       </c>
       <c r="N133" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="O133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
@@ -7134,6 +7299,7 @@
           <t>Kimyo omakase</t>
         </is>
       </c>
+      <c r="Q133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -7172,13 +7338,13 @@
         <v>4.379</v>
       </c>
       <c r="L134" t="n">
-        <v>82.7</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="M134" t="n">
         <v>4.648</v>
       </c>
       <c r="N134" t="n">
-        <v>93.8</v>
+        <v>93.5</v>
       </c>
       <c r="O134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
@@ -7186,6 +7352,7 @@
           <t>Ki Sushi</t>
         </is>
       </c>
+      <c r="Q134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -7224,13 +7391,13 @@
         <v>3.838</v>
       </c>
       <c r="L135" t="n">
-        <v>11.7</v>
+        <v>12.4</v>
       </c>
       <c r="M135" t="n">
         <v>4.207</v>
       </c>
       <c r="N135" t="n">
-        <v>49.2</v>
+        <v>51.1</v>
       </c>
       <c r="O135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
@@ -7238,6 +7405,7 @@
           <t>KOMA Sushi</t>
         </is>
       </c>
+      <c r="Q135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -7276,13 +7444,13 @@
         <v>4.053</v>
       </c>
       <c r="L136" t="n">
-        <v>28.9</v>
+        <v>30.1</v>
       </c>
       <c r="M136" t="n">
         <v>3.905</v>
       </c>
       <c r="N136" t="n">
-        <v>22.6</v>
+        <v>24.5</v>
       </c>
       <c r="O136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
@@ -7290,6 +7458,7 @@
           <t>Koju</t>
         </is>
       </c>
+      <c r="Q136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -7334,7 +7503,7 @@
         <v>4.599</v>
       </c>
       <c r="N137" t="n">
-        <v>90.3</v>
+        <v>90.2</v>
       </c>
       <c r="O137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
@@ -7342,6 +7511,7 @@
           <t>Hanaya Omakase</t>
         </is>
       </c>
+      <c r="Q137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -7380,13 +7550,13 @@
         <v>3.748</v>
       </c>
       <c r="L138" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="M138" t="n">
         <v>3.332</v>
       </c>
       <c r="N138" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="O138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
@@ -7394,6 +7564,7 @@
           <t>Jōji</t>
         </is>
       </c>
+      <c r="Q138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -7432,13 +7603,13 @@
         <v>4.437</v>
       </c>
       <c r="L139" t="n">
-        <v>88.3</v>
+        <v>88.7</v>
       </c>
       <c r="M139" t="n">
         <v>4.364</v>
       </c>
       <c r="N139" t="n">
-        <v>64.59999999999999</v>
+        <v>65.8</v>
       </c>
       <c r="O139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
@@ -7446,6 +7617,7 @@
           <t>Koete Omakase</t>
         </is>
       </c>
+      <c r="Q139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -7476,13 +7648,13 @@
         <v>4.28</v>
       </c>
       <c r="L140" t="n">
-        <v>60.4</v>
+        <v>61.8</v>
       </c>
       <c r="M140" t="n">
         <v>4.11</v>
       </c>
       <c r="N140" t="n">
-        <v>35.4</v>
+        <v>38.6</v>
       </c>
       <c r="O140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
@@ -7490,6 +7662,7 @@
           <t>Shinpi Omakase</t>
         </is>
       </c>
+      <c r="Q140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -7528,13 +7701,13 @@
         <v>3.466</v>
       </c>
       <c r="L141" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="M141" t="n">
         <v>3.544</v>
       </c>
       <c r="N141" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="O141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
@@ -7542,6 +7715,7 @@
           <t>Sushi Ann</t>
         </is>
       </c>
+      <c r="Q141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -7580,13 +7754,13 @@
         <v>4.166</v>
       </c>
       <c r="L142" t="n">
-        <v>43.7</v>
+        <v>44.6</v>
       </c>
       <c r="M142" t="n">
         <v>4.126</v>
       </c>
       <c r="N142" t="n">
-        <v>37.4</v>
+        <v>40.2</v>
       </c>
       <c r="O142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
@@ -7594,6 +7768,7 @@
           <t>Sushi Goda</t>
         </is>
       </c>
+      <c r="Q142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -7632,13 +7807,13 @@
         <v>4.248</v>
       </c>
       <c r="L143" t="n">
-        <v>54.8</v>
+        <v>55.9</v>
       </c>
       <c r="M143" t="n">
         <v>4.527</v>
       </c>
       <c r="N143" t="n">
-        <v>83.09999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="O143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
@@ -7646,6 +7821,7 @@
           <t>Sushi W - East Village</t>
         </is>
       </c>
+      <c r="Q143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -7670,16 +7846,17 @@
         <v>4.128</v>
       </c>
       <c r="L144" t="n">
-        <v>39.1</v>
+        <v>40.3</v>
       </c>
       <c r="M144" t="n">
         <v>4.053</v>
       </c>
       <c r="N144" t="n">
-        <v>29.7</v>
+        <v>32.1</v>
       </c>
       <c r="O144" t="inlineStr"/>
       <c r="P144" t="inlineStr"/>
+      <c r="Q144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -7718,13 +7895,13 @@
         <v>4.175</v>
       </c>
       <c r="L145" t="n">
-        <v>44.7</v>
+        <v>45.7</v>
       </c>
       <c r="M145" t="n">
         <v>4.326</v>
       </c>
       <c r="N145" t="n">
-        <v>62.1</v>
+        <v>63.6</v>
       </c>
       <c r="O145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
@@ -7732,6 +7909,7 @@
           <t>GOHAN SUSHI INC</t>
         </is>
       </c>
+      <c r="Q145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -7776,7 +7954,7 @@
         <v>4.469</v>
       </c>
       <c r="N146" t="n">
-        <v>77.40000000000001</v>
+        <v>77.2</v>
       </c>
       <c r="O146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
@@ -7784,6 +7962,7 @@
           <t>idashi Omakase</t>
         </is>
       </c>
+      <c r="Q146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -7818,13 +7997,13 @@
         <v>4.414</v>
       </c>
       <c r="L147" t="n">
-        <v>86.3</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="M147" t="n">
         <v>4.486</v>
       </c>
       <c r="N147" t="n">
-        <v>79.5</v>
+        <v>79.3</v>
       </c>
       <c r="O147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
@@ -7832,6 +8011,7 @@
           <t>Ishi Omakase Sushi &amp; Premium Sake</t>
         </is>
       </c>
+      <c r="Q147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -7870,13 +8050,13 @@
         <v>4.282</v>
       </c>
       <c r="L148" t="n">
-        <v>61.4</v>
+        <v>62.9</v>
       </c>
       <c r="M148" t="n">
         <v>4.352</v>
       </c>
       <c r="N148" t="n">
-        <v>63.6</v>
+        <v>64.7</v>
       </c>
       <c r="O148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
@@ -7884,6 +8064,7 @@
           <t>Oita Sushi</t>
         </is>
       </c>
+      <c r="Q148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -7922,13 +8103,13 @@
         <v>4.106</v>
       </c>
       <c r="L149" t="n">
-        <v>37.1</v>
+        <v>38.2</v>
       </c>
       <c r="M149" t="n">
         <v>4.173</v>
       </c>
       <c r="N149" t="n">
-        <v>44.6</v>
+        <v>46.2</v>
       </c>
       <c r="O149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
@@ -7936,6 +8117,7 @@
           <t>Uotora</t>
         </is>
       </c>
+      <c r="Q149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -7974,13 +8156,13 @@
         <v>4.309</v>
       </c>
       <c r="L150" t="n">
-        <v>68.5</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="M150" t="n">
         <v>4.301</v>
       </c>
       <c r="N150" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="O150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
@@ -7988,6 +8170,7 @@
           <t>Tanoshi Sushi Sake Bar</t>
         </is>
       </c>
+      <c r="Q150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -8026,7 +8209,7 @@
         <v>4.355</v>
       </c>
       <c r="L151" t="n">
-        <v>80.2</v>
+        <v>81.7</v>
       </c>
       <c r="M151" t="n">
         <v>4.427</v>
@@ -8040,6 +8223,7 @@
           <t>Kaki</t>
         </is>
       </c>
+      <c r="Q151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -8078,13 +8262,13 @@
         <v>3.929</v>
       </c>
       <c r="L152" t="n">
-        <v>19.3</v>
+        <v>19.9</v>
       </c>
       <c r="M152" t="n">
         <v>3.994</v>
       </c>
       <c r="N152" t="n">
-        <v>26.2</v>
+        <v>27.7</v>
       </c>
       <c r="O152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
@@ -8092,6 +8276,7 @@
           <t>Sushi Oku</t>
         </is>
       </c>
+      <c r="Q152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -8130,13 +8315,13 @@
         <v>4.294</v>
       </c>
       <c r="L153" t="n">
-        <v>65.5</v>
+        <v>66.7</v>
       </c>
       <c r="M153" t="n">
         <v>4.261</v>
       </c>
       <c r="N153" t="n">
-        <v>55.4</v>
+        <v>57.1</v>
       </c>
       <c r="O153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
@@ -8144,6 +8329,7 @@
           <t>Warabi Omakase</t>
         </is>
       </c>
+      <c r="Q153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -8178,22 +8364,15 @@
       <c r="J154" t="n">
         <v>59</v>
       </c>
-      <c r="K154" t="n">
-        <v>4.385</v>
-      </c>
-      <c r="L154" t="n">
-        <v>83.5</v>
-      </c>
-      <c r="M154" t="n">
-        <v>4.394</v>
-      </c>
-      <c r="N154" t="n">
-        <v>69</v>
-      </c>
       <c r="O154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Sushi Hayashi Williamsburg</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>Google rating 4.9 excluded — its Google place_id is claimed by another restaurant (both resolve to 'Sushi Hayashi Williamsburg'), so at least one match is wrong</t>
         </is>
       </c>
     </row>
@@ -8234,13 +8413,13 @@
         <v>4.178</v>
       </c>
       <c r="L155" t="n">
-        <v>45.7</v>
+        <v>46.8</v>
       </c>
       <c r="M155" t="n">
         <v>4.412</v>
       </c>
       <c r="N155" t="n">
-        <v>71.3</v>
+        <v>71.2</v>
       </c>
       <c r="O155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
@@ -8248,6 +8427,7 @@
           <t>Toka chef kitchen</t>
         </is>
       </c>
+      <c r="Q155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -8286,13 +8466,13 @@
         <v>4.345</v>
       </c>
       <c r="L156" t="n">
-        <v>77.7</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="M156" t="n">
         <v>3.738</v>
       </c>
       <c r="N156" t="n">
-        <v>10.8</v>
+        <v>11.4</v>
       </c>
       <c r="O156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
@@ -8300,6 +8480,7 @@
           <t>Sushi Sho</t>
         </is>
       </c>
+      <c r="Q156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -8338,7 +8519,7 @@
         <v>4.033</v>
       </c>
       <c r="L157" t="n">
-        <v>26.9</v>
+        <v>28</v>
       </c>
       <c r="M157" t="n">
         <v>3.619</v>
@@ -8352,6 +8533,7 @@
           <t>Muku</t>
         </is>
       </c>
+      <c r="Q157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -8390,13 +8572,13 @@
         <v>4.309</v>
       </c>
       <c r="L158" t="n">
-        <v>69</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="M158" t="n">
         <v>3.861</v>
       </c>
       <c r="N158" t="n">
-        <v>21</v>
+        <v>22.8</v>
       </c>
       <c r="O158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
@@ -8404,6 +8586,7 @@
           <t>Yamada</t>
         </is>
       </c>
+      <c r="Q158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -8442,13 +8625,13 @@
         <v>4.079</v>
       </c>
       <c r="L159" t="n">
-        <v>32</v>
+        <v>32.8</v>
       </c>
       <c r="M159" t="n">
         <v>3.917</v>
       </c>
       <c r="N159" t="n">
-        <v>24.1</v>
+        <v>26.1</v>
       </c>
       <c r="O159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
@@ -8456,6 +8639,7 @@
           <t>Odo East Village</t>
         </is>
       </c>
+      <c r="Q159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -8494,13 +8678,13 @@
         <v>3.344</v>
       </c>
       <c r="L160" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="M160" t="n">
         <v>3.14</v>
       </c>
       <c r="N160" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
@@ -8508,6 +8692,7 @@
           <t>Yoshoku</t>
         </is>
       </c>
+      <c r="Q160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -8546,13 +8731,13 @@
         <v>4.326</v>
       </c>
       <c r="L161" t="n">
-        <v>72.59999999999999</v>
+        <v>74.2</v>
       </c>
       <c r="M161" t="n">
         <v>3.766</v>
       </c>
       <c r="N161" t="n">
-        <v>12.8</v>
+        <v>13</v>
       </c>
       <c r="O161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
@@ -8560,6 +8745,7 @@
           <t>YUGIN</t>
         </is>
       </c>
+      <c r="Q161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -8598,13 +8784,13 @@
         <v>3.866</v>
       </c>
       <c r="L162" t="n">
-        <v>16.2</v>
+        <v>17.2</v>
       </c>
       <c r="M162" t="n">
         <v>3.573</v>
       </c>
       <c r="N162" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="O162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
@@ -8612,6 +8798,7 @@
           <t>Anbā</t>
         </is>
       </c>
+      <c r="Q162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -8650,13 +8837,13 @@
         <v>4.181</v>
       </c>
       <c r="L163" t="n">
-        <v>46.7</v>
+        <v>48.4</v>
       </c>
       <c r="M163" t="n">
         <v>3.911</v>
       </c>
       <c r="N163" t="n">
-        <v>23.6</v>
+        <v>25.5</v>
       </c>
       <c r="O163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
@@ -8664,6 +8851,7 @@
           <t>Enso Omakase</t>
         </is>
       </c>
+      <c r="Q163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -8702,13 +8890,13 @@
         <v>4.414</v>
       </c>
       <c r="L164" t="n">
-        <v>86.8</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="M164" t="n">
         <v>4.393</v>
       </c>
       <c r="N164" t="n">
-        <v>67.7</v>
+        <v>68.5</v>
       </c>
       <c r="O164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
@@ -8716,6 +8904,7 @@
           <t>Hear &amp; There</t>
         </is>
       </c>
+      <c r="Q164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -8754,13 +8943,13 @@
         <v>4.331</v>
       </c>
       <c r="L165" t="n">
-        <v>73.59999999999999</v>
+        <v>75.8</v>
       </c>
       <c r="M165" t="n">
         <v>4.173</v>
       </c>
       <c r="N165" t="n">
-        <v>44.1</v>
+        <v>45.7</v>
       </c>
       <c r="O165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
@@ -8768,6 +8957,7 @@
           <t>Kansha</t>
         </is>
       </c>
+      <c r="Q165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -8806,13 +8996,13 @@
         <v>4.34</v>
       </c>
       <c r="L166" t="n">
-        <v>76.59999999999999</v>
+        <v>78.5</v>
       </c>
       <c r="M166" t="n">
         <v>4.128</v>
       </c>
       <c r="N166" t="n">
-        <v>37.9</v>
+        <v>40.8</v>
       </c>
       <c r="O166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
@@ -8820,6 +9010,7 @@
           <t>Ikigai</t>
         </is>
       </c>
+      <c r="Q166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -8858,13 +9049,13 @@
         <v>3.966</v>
       </c>
       <c r="L167" t="n">
-        <v>21.3</v>
+        <v>22</v>
       </c>
       <c r="M167" t="n">
         <v>3.432</v>
       </c>
       <c r="N167" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="O167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
@@ -8872,6 +9063,7 @@
           <t>Sushi Ichimura</t>
         </is>
       </c>
+      <c r="Q167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -8910,13 +9102,13 @@
         <v>4.332</v>
       </c>
       <c r="L168" t="n">
-        <v>74.59999999999999</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="M168" t="n">
         <v>4.204</v>
       </c>
       <c r="N168" t="n">
-        <v>48.2</v>
+        <v>50</v>
       </c>
       <c r="O168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
@@ -8924,6 +9116,7 @@
           <t>Sushi Ishikawa</t>
         </is>
       </c>
+      <c r="Q168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -8962,13 +9155,13 @@
         <v>4.021</v>
       </c>
       <c r="L169" t="n">
-        <v>25.4</v>
+        <v>26.3</v>
       </c>
       <c r="M169" t="n">
         <v>3.533</v>
       </c>
       <c r="N169" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="O169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
@@ -8976,6 +9169,7 @@
           <t>Nakaji</t>
         </is>
       </c>
+      <c r="Q169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -9014,7 +9208,7 @@
         <v>4.271</v>
       </c>
       <c r="L170" t="n">
-        <v>58.9</v>
+        <v>60.8</v>
       </c>
       <c r="M170" t="n">
         <v>3.651</v>
@@ -9028,6 +9222,7 @@
           <t>69 Leonard Street</t>
         </is>
       </c>
+      <c r="Q170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -9066,13 +9261,13 @@
         <v>4.252</v>
       </c>
       <c r="L171" t="n">
-        <v>55.8</v>
+        <v>57.5</v>
       </c>
       <c r="M171" t="n">
         <v>3.85</v>
       </c>
       <c r="N171" t="n">
-        <v>19</v>
+        <v>20.7</v>
       </c>
       <c r="O171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
@@ -9080,6 +9275,7 @@
           <t>Shuko</t>
         </is>
       </c>
+      <c r="Q171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -9118,13 +9314,13 @@
         <v>4.022</v>
       </c>
       <c r="L172" t="n">
-        <v>25.9</v>
+        <v>26.9</v>
       </c>
       <c r="M172" t="n">
         <v>3.603</v>
       </c>
       <c r="N172" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="O172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
@@ -9132,6 +9328,7 @@
           <t>Kurumazushi</t>
         </is>
       </c>
+      <c r="Q172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -9170,13 +9367,13 @@
         <v>4.089</v>
       </c>
       <c r="L173" t="n">
-        <v>33.5</v>
+        <v>34.4</v>
       </c>
       <c r="M173" t="n">
         <v>3.56</v>
       </c>
       <c r="N173" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="O173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
@@ -9184,6 +9381,7 @@
           <t>icca</t>
         </is>
       </c>
+      <c r="Q173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -9214,6 +9412,7 @@
       <c r="H174" t="inlineStr"/>
       <c r="O174" t="inlineStr"/>
       <c r="P174" t="inlineStr"/>
+      <c r="Q174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -9252,13 +9451,13 @@
         <v>3.931</v>
       </c>
       <c r="L175" t="n">
-        <v>19.8</v>
+        <v>20.4</v>
       </c>
       <c r="M175" t="n">
         <v>3.534</v>
       </c>
       <c r="N175" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="O175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
@@ -9266,6 +9465,7 @@
           <t>Bar Masa</t>
         </is>
       </c>
+      <c r="Q175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -9304,13 +9504,13 @@
         <v>3.848</v>
       </c>
       <c r="L176" t="n">
-        <v>12.7</v>
+        <v>13.4</v>
       </c>
       <c r="M176" t="n">
         <v>3.447</v>
       </c>
       <c r="N176" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="O176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
@@ -9318,6 +9518,7 @@
           <t>Kappo Masa</t>
         </is>
       </c>
+      <c r="Q176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -9352,22 +9553,15 @@
       <c r="J177" t="n">
         <v>6</v>
       </c>
-      <c r="K177" t="n">
-        <v>3.264</v>
-      </c>
-      <c r="L177" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M177" t="n">
-        <v>3.045</v>
-      </c>
-      <c r="N177" t="n">
-        <v>0</v>
-      </c>
       <c r="O177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
           <t>Sushi Yoshi Time Square</t>
+        </is>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>Google rating 5 excluded — Google returned 'Sushi Yoshi Time Square', whose name similarity to 'Togyushi' is 0.29 — below the 0.80 trust threshold</t>
         </is>
       </c>
     </row>
@@ -9408,13 +9602,13 @@
         <v>4.175</v>
       </c>
       <c r="L178" t="n">
-        <v>45.2</v>
+        <v>46.2</v>
       </c>
       <c r="M178" t="n">
         <v>4.139</v>
       </c>
       <c r="N178" t="n">
-        <v>39</v>
+        <v>41.8</v>
       </c>
       <c r="O178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
@@ -9422,6 +9616,7 @@
           <t>Omi Omakase</t>
         </is>
       </c>
+      <c r="Q178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -9456,22 +9651,15 @@
       <c r="J179" t="n">
         <v>58</v>
       </c>
-      <c r="K179" t="n">
-        <v>3.906</v>
-      </c>
-      <c r="L179" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="M179" t="n">
-        <v>3.751</v>
-      </c>
-      <c r="N179" t="n">
-        <v>11.3</v>
-      </c>
       <c r="O179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
           <t>Himitsu - Omakase</t>
+        </is>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>Google rating 4.5 excluded — Google returned 'Himitsu - Omakase', whose name similarity to 'Himitsu Flushing' is 0.55 — below the 0.80 trust threshold</t>
         </is>
       </c>
     </row>
@@ -9512,13 +9700,13 @@
         <v>3.976</v>
       </c>
       <c r="L180" t="n">
-        <v>21.8</v>
+        <v>22.6</v>
       </c>
       <c r="M180" t="n">
         <v>3.831</v>
       </c>
       <c r="N180" t="n">
-        <v>16.4</v>
+        <v>17.4</v>
       </c>
       <c r="O180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
@@ -9526,6 +9714,7 @@
           <t>Kakurega Sushi</t>
         </is>
       </c>
+      <c r="Q180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -9560,22 +9749,15 @@
       <c r="J181" t="n">
         <v>865</v>
       </c>
-      <c r="K181" t="n">
-        <v>4.365</v>
-      </c>
-      <c r="L181" t="n">
-        <v>81.7</v>
-      </c>
-      <c r="M181" t="n">
-        <v>4.633</v>
-      </c>
-      <c r="N181" t="n">
-        <v>93.3</v>
-      </c>
       <c r="O181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
           <t>Wabi Nori Queens</t>
+        </is>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>Google rating 4.6 excluded — Google returned 'Wabi Nori Queens', whose name similarity to 'Kaizen (Wabi Nori Hand Roll Bar)' is 0.46 — below the 0.80 trust threshold</t>
         </is>
       </c>
     </row>
@@ -9616,13 +9798,13 @@
         <v>4.296</v>
       </c>
       <c r="L182" t="n">
-        <v>66.5</v>
+        <v>67.7</v>
       </c>
       <c r="M182" t="n">
         <v>4.393</v>
       </c>
       <c r="N182" t="n">
-        <v>68.2</v>
+        <v>69</v>
       </c>
       <c r="O182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
@@ -9630,6 +9812,7 @@
           <t>Izakaya Nana</t>
         </is>
       </c>
+      <c r="Q182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -9660,6 +9843,7 @@
       <c r="H183" t="inlineStr"/>
       <c r="O183" t="inlineStr"/>
       <c r="P183" t="inlineStr"/>
+      <c r="Q183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -9698,13 +9882,13 @@
         <v>4.356</v>
       </c>
       <c r="L184" t="n">
-        <v>80.7</v>
+        <v>82.3</v>
       </c>
       <c r="M184" t="n">
         <v>4.243</v>
       </c>
       <c r="N184" t="n">
-        <v>52.8</v>
+        <v>54.3</v>
       </c>
       <c r="O184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
@@ -9712,6 +9896,7 @@
           <t>Kaiyo Omakase</t>
         </is>
       </c>
+      <c r="Q184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -9750,13 +9935,13 @@
         <v>4.44</v>
       </c>
       <c r="L185" t="n">
-        <v>89.3</v>
+        <v>89.8</v>
       </c>
       <c r="M185" t="n">
         <v>4.187</v>
       </c>
       <c r="N185" t="n">
-        <v>45.6</v>
+        <v>47.8</v>
       </c>
       <c r="O185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
@@ -9764,6 +9949,7 @@
           <t>Omakase OSUKAA</t>
         </is>
       </c>
+      <c r="Q185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -9802,13 +9988,13 @@
         <v>4.149</v>
       </c>
       <c r="L186" t="n">
-        <v>41.6</v>
+        <v>43</v>
       </c>
       <c r="M186" t="n">
         <v>4.68</v>
       </c>
       <c r="N186" t="n">
-        <v>94.40000000000001</v>
+        <v>94</v>
       </c>
       <c r="O186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
@@ -9816,6 +10002,7 @@
           <t>Sapps</t>
         </is>
       </c>
+      <c r="Q186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -9854,13 +10041,13 @@
         <v>4.24</v>
       </c>
       <c r="L187" t="n">
-        <v>53.3</v>
+        <v>54.3</v>
       </c>
       <c r="M187" t="n">
         <v>4.563</v>
       </c>
       <c r="N187" t="n">
-        <v>86.7</v>
+        <v>87</v>
       </c>
       <c r="O187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
@@ -9868,6 +10055,7 @@
           <t>Hibino LIC</t>
         </is>
       </c>
+      <c r="Q187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -9906,13 +10094,13 @@
         <v>4.117</v>
       </c>
       <c r="L188" t="n">
-        <v>38.1</v>
+        <v>39.2</v>
       </c>
       <c r="M188" t="n">
         <v>4.333</v>
       </c>
       <c r="N188" t="n">
-        <v>63.1</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="O188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
@@ -9920,6 +10108,7 @@
           <t>Bushniwa</t>
         </is>
       </c>
+      <c r="Q188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -9958,13 +10147,13 @@
         <v>3.887</v>
       </c>
       <c r="L189" t="n">
-        <v>16.8</v>
+        <v>17.7</v>
       </c>
       <c r="M189" t="n">
         <v>3.758</v>
       </c>
       <c r="N189" t="n">
-        <v>11.8</v>
+        <v>12</v>
       </c>
       <c r="O189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
@@ -9972,6 +10161,7 @@
           <t>Nigiri</t>
         </is>
       </c>
+      <c r="Q189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -10010,13 +10200,13 @@
         <v>4.394</v>
       </c>
       <c r="L190" t="n">
-        <v>84.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="M190" t="n">
         <v>4.567</v>
       </c>
       <c r="N190" t="n">
-        <v>87.7</v>
+        <v>88</v>
       </c>
       <c r="O190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
@@ -10024,6 +10214,7 @@
           <t>Wagyu Place BBQ 和牛公馆</t>
         </is>
       </c>
+      <c r="Q190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -10058,22 +10249,15 @@
       <c r="J191" t="n">
         <v>3026</v>
       </c>
-      <c r="K191" t="n">
-        <v>4.614</v>
-      </c>
-      <c r="L191" t="n">
-        <v>97</v>
-      </c>
-      <c r="M191" t="n">
-        <v>4.534</v>
-      </c>
-      <c r="N191" t="n">
-        <v>84.09999999999999</v>
-      </c>
       <c r="O191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
           <t>NIKU X | Limitless Wagyu BBQ &amp; Seafood</t>
+        </is>
+      </c>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>Google rating 4.8 excluded — Google returned 'NIKU X | Limitless Wagyu BBQ &amp; Seafood', whose name similarity to 'Niku X NYC' is 0.32 — below the 0.80 trust threshold</t>
         </is>
       </c>
     </row>
@@ -10114,13 +10298,13 @@
         <v>4.379</v>
       </c>
       <c r="L192" t="n">
-        <v>82.2</v>
+        <v>83.3</v>
       </c>
       <c r="M192" t="n">
         <v>4.743</v>
       </c>
       <c r="N192" t="n">
-        <v>97.40000000000001</v>
+        <v>96.7</v>
       </c>
       <c r="O192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
@@ -10128,6 +10312,7 @@
           <t>Mikiya Wagyu Shabu House 味喜屋 | Flushing</t>
         </is>
       </c>
+      <c r="Q192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -10166,13 +10351,13 @@
         <v>4.41</v>
       </c>
       <c r="L193" t="n">
-        <v>85.3</v>
+        <v>85.5</v>
       </c>
       <c r="M193" t="n">
         <v>4.584</v>
       </c>
       <c r="N193" t="n">
-        <v>89.2</v>
+        <v>89.7</v>
       </c>
       <c r="O193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
@@ -10180,6 +10365,7 @@
           <t>Mikiya Wagyu Shabu House | Manhattan</t>
         </is>
       </c>
+      <c r="Q193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -10218,7 +10404,7 @@
         <v>4.715</v>
       </c>
       <c r="L194" t="n">
-        <v>99</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="M194" t="n">
         <v>4.979</v>
@@ -10232,6 +10418,7 @@
           <t>Chubby Cattle BBQ | New York</t>
         </is>
       </c>
+      <c r="Q194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -10270,7 +10457,7 @@
         <v>4.291</v>
       </c>
       <c r="L195" t="n">
-        <v>64.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="M195" t="n">
         <v>4.608</v>
@@ -10284,6 +10471,7 @@
           <t>Y Space BBQ 烤肉火焱星</t>
         </is>
       </c>
+      <c r="Q195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -10322,13 +10510,13 @@
         <v>4.316</v>
       </c>
       <c r="L196" t="n">
-        <v>70.09999999999999</v>
+        <v>72</v>
       </c>
       <c r="M196" t="n">
         <v>4.486</v>
       </c>
       <c r="N196" t="n">
-        <v>79</v>
+        <v>78.8</v>
       </c>
       <c r="O196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
@@ -10336,6 +10524,7 @@
           <t>Wagyu Yama Yakiniku &amp; Seafood Shabu 牛帮主和牛烤肉海鲜火锅自助</t>
         </is>
       </c>
+      <c r="Q196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -10370,22 +10559,15 @@
       <c r="J197" t="n">
         <v>359</v>
       </c>
-      <c r="K197" t="n">
-        <v>3.686</v>
-      </c>
-      <c r="L197" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="M197" t="n">
-        <v>4.171</v>
-      </c>
-      <c r="N197" t="n">
-        <v>43.3</v>
-      </c>
       <c r="O197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
           <t>Gyu-Ichiro Japanese BBQ</t>
+        </is>
+      </c>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>Google rating 4 excluded — its Google place_id is claimed by another restaurant (both resolve to 'Gyu-Ichiro Japanese BBQ'), so at least one match is wrong</t>
         </is>
       </c>
     </row>
@@ -10422,22 +10604,15 @@
       <c r="J198" t="n">
         <v>171</v>
       </c>
-      <c r="K198" t="n">
-        <v>3.904</v>
-      </c>
-      <c r="L198" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="M198" t="n">
-        <v>4.201</v>
-      </c>
-      <c r="N198" t="n">
-        <v>47.7</v>
-      </c>
       <c r="O198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
           <t>Hiyake Yakiniku BBQ</t>
+        </is>
+      </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>Google rating 4.3 excluded — Google returned 'Hiyake Yakiniku BBQ', whose name similarity to 'Hiyake Omakase (Williamsburg)' is 0.52 — below the 0.80 trust threshold</t>
         </is>
       </c>
     </row>
@@ -10474,22 +10649,15 @@
       <c r="J199" t="n">
         <v>359</v>
       </c>
-      <c r="K199" t="n">
-        <v>3.686</v>
-      </c>
-      <c r="L199" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="M199" t="n">
-        <v>4.171</v>
-      </c>
-      <c r="N199" t="n">
-        <v>43.3</v>
-      </c>
       <c r="O199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
           <t>Gyu-Ichiro Japanese BBQ</t>
+        </is>
+      </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>Google rating 4 excluded — its Google place_id is claimed by another restaurant (both resolve to 'Gyu-Ichiro Japanese BBQ'), so at least one match is wrong</t>
         </is>
       </c>
     </row>
@@ -10530,13 +10698,13 @@
         <v>3.447</v>
       </c>
       <c r="L200" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="M200" t="n">
         <v>3.66</v>
       </c>
       <c r="N200" t="n">
-        <v>9.699999999999999</v>
+        <v>10.3</v>
       </c>
       <c r="O200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
@@ -10544,6 +10712,7 @@
           <t>Nikushou Sakai</t>
         </is>
       </c>
+      <c r="Q200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -10582,7 +10751,7 @@
         <v>4.447</v>
       </c>
       <c r="L201" t="n">
-        <v>89.8</v>
+        <v>90.3</v>
       </c>
       <c r="M201" t="n">
         <v>4.874</v>
@@ -10596,6 +10765,7 @@
           <t>Umiya Sushi</t>
         </is>
       </c>
+      <c r="Q201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -10634,13 +10804,13 @@
         <v>4.185</v>
       </c>
       <c r="L202" t="n">
-        <v>47.7</v>
+        <v>49.5</v>
       </c>
       <c r="M202" t="n">
         <v>4.72</v>
       </c>
       <c r="N202" t="n">
-        <v>96.40000000000001</v>
+        <v>95.7</v>
       </c>
       <c r="O202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
@@ -10648,6 +10818,7 @@
           <t>Asuka Sushi</t>
         </is>
       </c>
+      <c r="Q202" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
